--- a/templates/pds_template2025.xlsx
+++ b/templates/pds_template2025.xlsx
@@ -5038,4690 +5038,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="50" dropStyle="combo" dx="16" fmlaRange="Q11:Q216" noThreeD="1" sel="4" val="3"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Label"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18820" name="AutoShape 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084490000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11677650" y="2638425"/>
-          <a:ext cx="2314575" cy="1066800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>111779</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>43786</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>148300</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>274220</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7287" name="Rectangle 119">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000771C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8814165" y="2780059"/>
-          <a:ext cx="36521" cy="230434"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>486117</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>31018</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>522638</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>248650</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7294" name="Rectangle 126">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E1C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9188503" y="3061700"/>
-          <a:ext cx="36521" cy="217632"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>120909</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>5448</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>157430</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>235882</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7296" name="Rectangle 128">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000801C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8823295" y="3330539"/>
-          <a:ext cx="36521" cy="230434"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>172146</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>18182</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>199537</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>261417</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7300" name="Rectangle 132">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000841C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9480669" y="2754455"/>
-          <a:ext cx="27391" cy="243235"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>583004</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>56588</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>592134</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>235848</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7302" name="Rectangle 134">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000861C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9891527" y="2792861"/>
-          <a:ext cx="9130" cy="473669"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>77300</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>31018</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>113821</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>248650</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7306" name="Rectangle 138">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A1C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9991959" y="3061700"/>
-          <a:ext cx="36521" cy="217632"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>509963</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>5448</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>546484</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>235882</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7310" name="Rectangle 142">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E1C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9818486" y="3330539"/>
-          <a:ext cx="36521" cy="230434"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
-            <a:cs typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18831" name="Text Box 168">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F490000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7648575" y="2247900"/>
-          <a:ext cx="0" cy="476250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>361860</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>23323</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>32635</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>138356</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18833" name="Rectangle 188">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091490000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3213010" y="1121873"/>
-          <a:ext cx="102575" cy="115033"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>326819</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>59748</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="TextBox 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7439025" y="9525"/>
-          <a:ext cx="1107869" cy="259773"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1200" b="1" i="1">
-            <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>41414</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>16564</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1010480</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>265042</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="TextBox 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="41414" y="16564"/>
-          <a:ext cx="1134718" cy="447261"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1"/>
-            <a:t>CS</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0"/>
-            <a:t> Form No. 212</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" i="1" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Revised 2025</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="900" b="0" i="1">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>596900</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1055" name="Drop Down 31" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1055"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData fLocksWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1045" name="Check Box 21" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Filipino</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1046" name="Check Box 22" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Dual Citizenship</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>914400</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1049" name="Check Box 25" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Male</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1050" name="Check Box 26" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Female</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>266700</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>914400</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1058" name="Check Box 34" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Single</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>292100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1059" name="Check Box 35" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Married</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>139700</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>914400</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1060" name="Check Box 36" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Widowed</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>914400</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1061" name="Check Box 37" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Other/s:</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1062" name="Check Box 38" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> Separated</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>254000</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>723900</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1063" name="Check Box 39" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t>by birth </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>723900</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>254000</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>596900</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1064" name="Check Box 40" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t>by naturalization </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="195601"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9327" name="Rectangle 111">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00006F240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4600575" y="6991350"/>
-          <a:ext cx="38472" cy="176972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="195601"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9329" name="Rectangle 113">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000071240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4733925" y="6991350"/>
-          <a:ext cx="38472" cy="176972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="195601"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9331" name="Rectangle 115">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000073240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4953000" y="6991350"/>
-          <a:ext cx="38472" cy="176972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="195601"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9333" name="Rectangle 117">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000075240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5334000" y="6991350"/>
-          <a:ext cx="38472" cy="176972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="195601"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9335" name="Rectangle 119">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000077240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5172075" y="6991350"/>
-          <a:ext cx="38472" cy="176972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>207066</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>37270</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>418270</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9316" name="Text Box 100">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000064240000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5772979" y="7541313"/>
-          <a:ext cx="1242391" cy="1532283"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Passport-sized unfiltered digital picture taken within </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>the last  6 months</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-PH" sz="700" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>4.5 cm. X 3.5 cm</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>222250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1149350</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="Straight Connector 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm flipV="1">
-          <a:off x="2673350" y="11296650"/>
-          <a:ext cx="1549400" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>139700</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4097" name="Check Box 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>558800</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>342900</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4098" name="Check Box 2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>139700</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4099" name="Check Box 3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>558800</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>342900</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4100" name="Check Box 4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4101" name="Check Box 5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4102" name="Check Box 6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4103" name="Check Box 7" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>63500</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>406400</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4104" name="Check Box 8" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4105" name="Check Box 9" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>101600</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>444500</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4106" name="Check Box 10" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>101600</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>342900</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4107" name="Check Box 11" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000B100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>101600</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>444500</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4108" name="Check Box 12" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000C100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4109" name="Check Box 13" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000D100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4110" name="Check Box 14" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000E100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4111" name="Check Box 15" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4111"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000F100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4112" name="Check Box 16" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4112"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000010100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4113" name="Check Box 17" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4113"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000011100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4114" name="Check Box 18" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4114"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000012100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4115" name="Check Box 19" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4115"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000013100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4116" name="Check Box 20" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4116"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000014100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1384300</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1219200</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>228600</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4121" name="Label 25" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4121"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000019100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:noFill/>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Arial" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Arial" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fLocksWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>368300</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4122" name="Check Box 26" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4122"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001A100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4123" name="Check Box 27" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4123"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001B100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>139700</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4124" name="Check Box 28" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4124"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001C100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4125" name="Check Box 29" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4125"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001D100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
-                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
-                </a:rPr>
-                <a:t> NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -15518,277 +10834,8 @@
   <pageMargins left="0.15" right="0.12" top="0.36" bottom="0.12" header="0.24" footer="0.12"/>
   <pageSetup paperSize="269" scale="73" orientation="portrait" r:id="rId206"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId207"/>
-  <legacyDrawing r:id="rId208"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId209" name="Drop Down 31">
-              <controlPr locked="0" defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>596900</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId210" name="Check Box 21">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId211" name="Check Box 22">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId212" name="Check Box 25">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>914400</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId213" name="Check Box 26">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId214" name="Check Box 34">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>266700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>914400</xdr:colOff>
-                    <xdr:row>17</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId215" name="Check Box 35">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>292100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>17</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId216" name="Check Box 36">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>139700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>914400</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId217" name="Check Box 37">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>914400</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId218" name="Check Box 38">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>152400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId219" name="Check Box 39">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>254000</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>723900</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>101600</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId220" name="Check Box 40">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>723900</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>254000</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>596900</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
+    <mc:Choice Requires="x14"/>
   </mc:AlternateContent>
 </worksheet>
 </file>
@@ -18724,563 +13771,8 @@
   <pageMargins left="0.11811023622047245" right="0" top="0.35433070866141736" bottom="0" header="0.15748031496062992" footer="0"/>
   <pageSetup paperSize="269" scale="83" orientation="portrait" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4097" r:id="rId5" name="Check Box 1">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>139700</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4098" r:id="rId6" name="Check Box 2">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>558800</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>342900</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4099" r:id="rId7" name="Check Box 3">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>139700</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4100" r:id="rId8" name="Check Box 4">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>558800</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>342900</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4101" r:id="rId9" name="Check Box 5">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4102" r:id="rId10" name="Check Box 6">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4103" r:id="rId11" name="Check Box 7">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4104" r:id="rId12" name="Check Box 8">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>63500</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>406400</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4105" r:id="rId13" name="Check Box 9">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4106" r:id="rId14" name="Check Box 10">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>101600</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>444500</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4107" r:id="rId15" name="Check Box 11">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>101600</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>342900</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4108" r:id="rId16" name="Check Box 12">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>101600</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>444500</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4109" r:id="rId17" name="Check Box 13">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>36</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>37</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4110" r:id="rId18" name="Check Box 14">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>36</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>37</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4111" r:id="rId19" name="Check Box 15">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>42</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>43</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4112" r:id="rId20" name="Check Box 16">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4113" r:id="rId21" name="Check Box 17">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4114" r:id="rId22" name="Check Box 18">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>42</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
-                    <xdr:row>43</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4115" r:id="rId23" name="Check Box 19">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4116" r:id="rId24" name="Check Box 20">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4121" r:id="rId25" name="Label 25">
-              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>1384300</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>1219200</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>228600</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4122" r:id="rId26" name="Check Box 26">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>368300</xdr:colOff>
-                    <xdr:row>31</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4123" r:id="rId27" name="Check Box 27">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>31</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4124" r:id="rId28" name="Check Box 28">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>139700</xdr:colOff>
-                    <xdr:row>32</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4125" r:id="rId29" name="Check Box 29">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>10</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>32</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>11</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
+    <mc:Choice Requires="x14"/>
   </mc:AlternateContent>
 </worksheet>
 </file>
